--- a/stories/arbres/ATOM-VIV.ANI.002-06.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Étienne est à la ferme avec papa. Un coq chante. Une poule picore. Un poussin suit. Papa dit : coq, poule, poussin. Ce sont trois noms. Étienne répète. Parce qu'il a nommé, il retient. Plus loin, un cheval hennit. Une jument marche. Un poulain suit. Papa dit : cheval, jument, poulain. Ce sont trois noms de la famille. Étienne dit les trois noms. Coq, poule, poussin. Cheval, jument, poulain. Papa sourit. Étienne sent l'herbe.</t>
+          <t>Étienne est à la ferme avec papa. Un coq chante. Une poule picore. Un poussin suit. Coq, poule, poussin. Ce sont trois noms. Étienne répète. Parce qu'il a nommé, il retient. Plus loin, un cheval hennit. Une jument marche. Un poulain suit. Cheval, jument, poulain. Ce sont trois noms de la famille. Étienne dit les trois noms. Coq, poule, poussin. Cheval, jument, poulain. Papa sourit. Étienne sent l'herbe.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Étienne est à la ferme avec papa. Un coq chante. Une poule picore. Un poussin suit.
+papa|Coq, poule, poussin. Ce sont trois noms.
+narrateur|Étienne répète. Parce qu'il a nommé, il retient. Plus loin, un cheval hennit. Une jument marche. Un poulain suit.
+papa|Cheval, jument, poulain. Ce sont trois noms de la famille.
+narrateur|Étienne dit les trois noms. Coq, poule, poussin. Cheval, jument, poulain. Papa sourit. Étienne sent l'herbe.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Étienne a dit les trois noms. Coq, poule, poussin. Cheval, jument, poulain.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Étienne caresse l'herbe. Papa tient sa main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.002-06.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Étienne dit les trois noms. Coq, poule, poussin. Cheval, jument, poulain. Papa sourit. Étienne sent l'herbe.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Étienne a dit les trois noms. Coq, poule, poussin. Cheval, jument, poulain.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1847,7 @@
           <t>narrateur|Étienne caresse l'herbe. Papa tient sa main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.002-06.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Étienne dit les trois noms à la ferme</t>
+          <t>Le veau et le seau</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël veut voir le veau. Le seau de zinc cliquette. Il le pose. Taureau, vache et veau sont au calme. Le veau boit.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Étienne est à la ferme avec papa. Un coq chante. Une poule picore. Un poussin suit. Coq, poule, poussin. Ce sont trois noms. Étienne répète. Parce qu'il a nommé, il retient. Plus loin, un cheval hennit. Une jument marche. Un poulain suit. Cheval, jument, poulain. Ce sont trois noms de la famille. Étienne dit les trois noms. Coq, poule, poussin. Cheval, jument, poulain. Papa sourit. Étienne sent l'herbe.</t>
+          <t>Le zinc du seau est froid, tout gris. Il sent encore le lait tiède. La laiterie est sombre, un peu fraîche. Raphaël vit ici, avec papa. Une mouche tourne près de la fenêtre. Papa, je veux voir le veau. Le petit de la vache ? Oui. Je veux lui parler. En ce moment, papa tend le seau. Raphaël le prend à deux mains. Le seau cliquette contre son genou. Cling, cling, sur le seuil de pierre. Il fait trop de bruit. On le pose ? Oui. Raphaël pose le seau près du mur. Le zinc se tait d'un coup. Merci, Raphaël. Maintenant on peut avancer doux. Ils marchent vers l'enclos. L'herbe sent le lait et le foin. Un taureau brun reste au fond, calme. Le taureau. Oui. On le salue de loin. Une vache lèche une barre de sel. La vache ! Tu la vois bien ? Oui. Le veau est où ? Près d'elle, tout contre. Un veau roux lève le museau. Le veau ! Taureau, vache, veau. Trois noms de la famille. Raphaël s'accroupit près de la barrière. Bonjour, petit. Le veau avance, sans bruit. Sans le seau, il vient. Raphaël reste accroupi, sans bouger le seau. Le veau passe la langue sur le bois. Il a soif. La vache l'a déjà nourri. Toi, tu lui parles. Le taureau baisse la tête au fond. Il broute, sans s'approcher. Il est grand. Oui. On le salue de loin. Une goutte de lait a séché sur le zinc. Le seau attend au mur. Il ne cliquette plus.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Étienne est à la ferme avec papa. Un coq chante. Une poule picore. Un poussin suit. Papa dit : coq, poule, poussin. Ce sont &lt;emphasis level="moderate"&gt;trois&lt;/emphasis&gt; noms. Étienne répète. Parce qu'il a nommé, il retient. Plus loin, un cheval hennit. Une jument marche. Un poulain suit. Papa dit : cheval, jument, poulain. Ce sont trois noms de la famille. Étienne dit les trois noms. Coq, poule, poussin. Cheval, jument, poulain. Papa sourit. Étienne sent l'herbe.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le zinc du seau est froid, tout gris. Il sent encore le lait tiède. La laiterie est sombre, un peu fraîche. Raphaël vit ici, avec papa. Une mouche tourne près de la fenêtre. Papa, je veux voir le veau. Le petit de la vache ? Oui. Je veux lui parler. En ce moment, papa tend le seau. Raphaël le prend à deux mains. Le seau cliquette contre son genou. Cling, cling, sur le seuil de pierre. Il fait trop de bruit. On le pose ? Oui. Raphaël pose le seau près du mur. Le zinc se tait d'un coup. Merci, Raphaël. Maintenant on peut avancer doux. Ils marchent vers l'enclos. L'herbe sent le lait et le foin. Un taureau brun reste au fond, calme. Le taureau. Oui. On le salue de loin. Une vache lèche une barre de sel. La vache ! Tu la vois bien ? Oui. Le veau est où ? Près d'elle, tout contre. Un veau roux lève le museau. Le veau ! Taureau, vache, veau. Trois noms de la famille. Raphaël s'accroupit près de la barrière. Bonjour, petit. Le veau avance, sans bruit. Sans le seau, il vient. Raphaël reste accroupi, sans bouger le seau. Le veau passe la langue sur le bois. Il a soif. La vache l'a déjà nourri. Toi, tu lui parles. Le taureau baisse la tête au fond. Il broute, sans s'approcher. Il est grand. Oui. On le salue de loin. Une goutte de lait a séché sur le zinc. Le seau attend au mur. Il ne cliquette plus.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,11 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Étienne est à la ferme avec papa. Un coq chante. Une poule picore. Un poussin suit.
-papa|Coq, poule, poussin. Ce sont trois noms.
-narrateur|Étienne répète. Parce qu'il a nommé, il retient. Plus loin, un cheval hennit. Une jument marche. Un poulain suit.
-papa|Cheval, jument, poulain. Ce sont trois noms de la famille.
-narrateur|Étienne dit les trois noms. Coq, poule, poussin. Cheval, jument, poulain. Papa sourit. Étienne sent l'herbe.</t>
+          <t>narrateur|Le zinc du seau est froid, tout gris.
+narrateur|Il sent encore le lait tiède.
+narrateur|La laiterie est sombre, un peu fraîche.
+narrateur|Raphaël vit ici, avec papa.
+narrateur|Une mouche tourne près de la fenêtre.
+enfant-m|Papa, je veux voir le veau.
+papa|Le petit de la vache ?
+enfant-m|Oui.
+enfant-m|Je veux lui parler.
+narrateur|En ce moment, papa tend le seau.
+narrateur|Raphaël le prend à deux mains.
+narrateur|Le seau cliquette contre son genou.
+narrateur|Cling, cling, sur le seuil de pierre.
+enfant-m|Il fait trop de bruit.
+papa|On le pose ?
+enfant-m|Oui.
+narrateur|Raphaël pose le seau près du mur.
+narrateur|Le zinc se tait d'un coup.
+papa|Merci, Raphaël.
+papa|Maintenant on peut avancer doux.
+narrateur|Ils marchent vers l'enclos.
+narrateur|L'herbe sent le lait et le foin.
+narrateur|Un taureau brun reste au fond, calme.
+enfant-m|Le taureau.
+papa|Oui.
+papa|On le salue de loin.
+narrateur|Une vache lèche une barre de sel.
+enfant-m|La vache !
+papa|Tu la vois bien ?
+enfant-m|Oui.
+enfant-m|Le veau est où ?
+papa|Près d'elle, tout contre.
+narrateur|Un veau roux lève le museau.
+enfant-m|Le veau !
+papa|Taureau, vache, veau.
+papa|Trois noms de la famille.
+narrateur|Raphaël s'accroupit près de la barrière.
+enfant-m|Bonjour, petit.
+narrateur|Le veau avance, sans bruit.
+papa|Sans le seau, il vient.
+narrateur|Raphaël reste accroupi, sans bouger le seau.
+narrateur|Le veau passe la langue sur le bois.
+enfant-m|Il a soif.
+papa|La vache l'a déjà nourri.
+papa|Toi, tu lui parles.
+narrateur|Le taureau baisse la tête au fond.
+narrateur|Il broute, sans s'approcher.
+enfant-m|Il est grand.
+papa|Oui.
+papa|On le salue de loin.
+narrateur|Une goutte de lait a séché sur le zinc.
+papa|Le seau attend au mur.
+enfant-m|Il ne cliquette plus.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,12 +1408,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le coq, la poule, et le petit. Quel est le petit ?</t>
+          <t>Le petit de la vache, c'est qui ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le coq, la poule, et le petit. Quel est le petit ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le petit de la vache, c'est qui ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,12 +1423,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>poussin</t>
+          <t>veau</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>poussin | le poussin | petit | le petit</t>
+          <t>veau | le veau | un veau</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1383,7 +1443,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Le petit du coq et de la poule. Qui est-ce ?</t>
+          <t>C'est le veau. Quel est le petit de la vache ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1432,7 +1492,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,10 +1564,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le coq, la poule, et le petit. Quel est le petit ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Le petit de la vache, c'est qui ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,12 +1591,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Étienne a dit les trois noms. Coq, poule, poussin. Cheval, jument, poulain.</t>
+          <t>Le veau passe la langue sur le bois. Le bois est rêche, encore humide. Il a une langue rêche. Oui. C'est le petit de la vache. On lui laisse le calme ? Oui, papa. Derrière eux, le seau reste muet. Il ne cliquette plus.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Étienne a dit les &lt;emphasis level="moderate"&gt;trois&lt;/emphasis&gt; noms. Coq, poule, poussin. Cheval, jument, poulain.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le veau passe la langue sur le bois. Le bois est rêche, encore humide. Il a une langue rêche. Oui. C'est le petit de la vache. On lui laisse le calme ? Oui, papa. Derrière eux, le seau reste muet. Il ne cliquette plus.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1600,7 +1659,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1676,10 +1735,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Étienne a dit les trois noms. Coq, poule, poussin. Cheval, jument, poulain.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le veau passe la langue sur le bois.
+narrateur|Le bois est rêche, encore humide.
+enfant-m|Il a une langue rêche.
+papa|Oui.
+papa|C'est le petit de la vache.
+papa|On lui laisse le calme ?
+enfant-m|Oui, papa.
+narrateur|Derrière eux, le seau reste muet.
+enfant-m|Il ne cliquette plus.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,12 +1770,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Étienne caresse l'herbe. Papa tient sa main.</t>
+          <t>Ils reprennent le seau, tout doux. Raphaël le tient loin du genou. Le zinc ne dit plus rien. Le taureau est resté au fond. La vache lèche encore le sel. Tu as vu les trois ? Taureau, vache, veau. Raphaël pose le seau dans la laiterie. Sur la pierre froide. Loin du genou. La fenêtre laisse un carré de jour sur le zinc.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Étienne caresse l'herbe. Papa tient sa &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils reprennent le seau, tout doux. Raphaël le tient loin du genou. Le zinc ne dit plus rien. Le taureau est resté au fond. La vache lèche encore le sel. Tu as vu les trois ? Taureau, vache, veau. Raphaël pose le seau dans la laiterie. Sur la pierre froide. Loin du genou. La fenêtre laisse un carré de jour sur le zinc.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1772,7 +1838,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1844,10 +1910,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Étienne caresse l'herbe. Papa tient sa main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils reprennent le seau, tout doux.
+narrateur|Raphaël le tient loin du genou.
+narrateur|Le zinc ne dit plus rien.
+enfant-m|Le taureau est resté au fond.
+papa|La vache lèche encore le sel.
+papa|Tu as vu les trois ?
+enfant-m|Taureau, vache, veau.
+narrateur|Raphaël pose le seau dans la laiterie.
+papa|Sur la pierre froide.
+enfant-m|Loin du genou.
+narrateur|La fenêtre laisse un carré de jour sur le zinc.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,12 +1947,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Il a bu, papa. Sans le bruit. Le veau boit, et le seau se tait.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Il a bu, papa. Sans le bruit. Le veau boit, et le seau se tait.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1933,14 +2008,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2012,10 +2087,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|Il a bu, papa.
+papa|Sans le bruit.
+narrateur|Le veau boit, et le seau se tait.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2148,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.002-06.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.002-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ferme</t>
+          <t>ferme, laiterie, enclos du veau</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Étienne, papa</t>
+          <t>Raphaël, papa</t>
         </is>
       </c>
     </row>
